--- a/frontend/sample-data/demo-boreholes.xlsx
+++ b/frontend/sample-data/demo-boreholes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://basalt365online-my.sharepoint.com/personal/fussmannd_basalt-online_de/Documents/Recruiting_OD/Material_Fallbeispiele/CASE 2 - Bohrkerndaten Integration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20ECABF3-676C-4179-B345-AF57C0471FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B914E5D4-C0CA-427A-B618-D85076904BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2340" windowWidth="29040" windowHeight="15720" firstSheet="1" xr2:uid="{F24A5098-16F1-4D2A-8416-5B3A4B23A45A}"/>
+    <workbookView xWindow="28680" yWindow="-2340" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F24A5098-16F1-4D2A-8416-5B3A4B23A45A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hellberg-GWM1" sheetId="1" r:id="rId1"/>
@@ -34,28 +34,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -738,70 +716,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1136,27 +1050,25 @@
     <col min="9" max="9" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45">
+    <row r="1" spans="1:9" ht="23.45" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="21" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="H1" s="21"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="14.45" customHeight="1">
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" ht="18" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="21"/>
       <c r="I3" s="21"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="14.45" customHeight="1">
       <c r="H4" s="21"/>
       <c r="I4" s="21"/>
     </row>
@@ -1176,7 +1088,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
     </row>
-    <row r="6" spans="1:9" ht="28.9">
+    <row r="6" spans="1:9" ht="28.9" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1104,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="14.45" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1208,26 +1120,26 @@
       <c r="H7" s="21"/>
       <c r="I7" s="21"/>
     </row>
-    <row r="8" spans="1:9" ht="28.9">
+    <row r="8" spans="1:9" ht="28.9" customHeight="1">
       <c r="E8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" ht="18" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
     </row>
-    <row r="10" spans="1:9" ht="15.6">
+    <row r="10" spans="1:9" ht="15.6" customHeight="1">
       <c r="A10" s="1"/>
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
@@ -1238,7 +1150,7 @@
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="15">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -2645,9 +2557,6 @@
       <c r="I120" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:I11"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -2670,31 +2579,29 @@
     <col min="9" max="9" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45">
+    <row r="1" spans="1:9" ht="23.45" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="21" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="H1" s="21"/>
       <c r="I1" s="21"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="14.45" customHeight="1">
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" ht="18">
+    <row r="3" spans="1:9" ht="18" customHeight="1">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="21"/>
       <c r="I3" s="21"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" ht="14.45" customHeight="1">
       <c r="H4" s="21"/>
       <c r="I4" s="21"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" ht="14.45" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
@@ -2710,7 +2617,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
     </row>
-    <row r="6" spans="1:9" ht="28.9">
+    <row r="6" spans="1:9" ht="28.9" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>6</v>
       </c>
@@ -2726,7 +2633,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" ht="14.45" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -2742,26 +2649,26 @@
       <c r="H7" s="21"/>
       <c r="I7" s="21"/>
     </row>
-    <row r="8" spans="1:9" ht="28.9">
+    <row r="8" spans="1:9" ht="28.9" customHeight="1">
       <c r="E8" s="20" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
     </row>
-    <row r="9" spans="1:9" ht="18">
+    <row r="9" spans="1:9" ht="18" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
     </row>
-    <row r="10" spans="1:9" ht="15.6">
+    <row r="10" spans="1:9" ht="15.6" customHeight="1">
       <c r="A10" s="1"/>
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="14.45" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
@@ -2772,7 +2679,7 @@
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="15">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -4187,9 +4094,6 @@
       <c r="I120" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:I11"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -4205,6 +4109,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bbd9614c-a230-424e-b68d-4d9b38652f87" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07747c92-9f66-48a8-9308-d9b4351bd7c4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C65865D628F93B489FA2B7F1BA836014" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="36d8c53392b6e8640b7f5a239be2caeb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="07747c92-9f66-48a8-9308-d9b4351bd7c4" xmlns:ns3="bbd9614c-a230-424e-b68d-4d9b38652f87" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39f71d0db23b0fe86f26fe3a0ca0bd2b" ns2:_="" ns3:_="">
     <xsd:import namespace="07747c92-9f66-48a8-9308-d9b4351bd7c4"/>
@@ -4405,25 +4320,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bbd9614c-a230-424e-b68d-4d9b38652f87" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="07747c92-9f66-48a8-9308-d9b4351bd7c4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B0D87D9-CF91-48C7-8A9F-86CAE10AA1A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E477EA-1BF5-408C-A608-BCB938A2B3A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC5CB9A-A6E9-44F1-8422-44E207C8DDE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC5CB9A-A6E9-44F1-8422-44E207C8DDE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2E477EA-1BF5-408C-A608-BCB938A2B3A9}"/>
 </file>